--- a/analysis/booster_cause_analysis.xlsx
+++ b/analysis/booster_cause_analysis.xlsx
@@ -992,11 +992,11 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>58_a</t>
+          <t>2_b</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -1005,25 +1005,25 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>2050</v>
+        <v>2045</v>
       </c>
       <c r="H2" t="n">
-        <v>2050</v>
+        <v>2045</v>
       </c>
       <c r="I2" t="n">
-        <v>61.78125860955673</v>
+        <v>72.70748558974221</v>
       </c>
       <c r="J2" t="n">
-        <v>61.78125860955673</v>
+        <v>72.70748558974221</v>
       </c>
       <c r="K2" t="n">
         <v>100</v>
       </c>
       <c r="L2" t="n">
-        <v>7.28118475892359</v>
+        <v>11.52058370585532</v>
       </c>
       <c r="M2" t="n">
-        <v>7.375125740250011</v>
+        <v>11.01168039290185</v>
       </c>
       <c r="N2" t="n">
         <v>15</v>
@@ -1160,11 +1160,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2_b</t>
+          <t>13_b</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -1173,25 +1173,25 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>2045</v>
+        <v>2050</v>
       </c>
       <c r="H5" t="n">
-        <v>2045</v>
+        <v>2050</v>
       </c>
       <c r="I5" t="n">
-        <v>72.70748558974221</v>
+        <v>72.94993796812167</v>
       </c>
       <c r="J5" t="n">
-        <v>72.70748558974221</v>
+        <v>72.94993796812167</v>
       </c>
       <c r="K5" t="n">
         <v>100</v>
       </c>
       <c r="L5" t="n">
-        <v>11.52058370585532</v>
+        <v>12.7026408063513</v>
       </c>
       <c r="M5" t="n">
-        <v>11.01168039290185</v>
+        <v>12.20616628491663</v>
       </c>
       <c r="N5" t="n">
         <v>15</v>
@@ -1216,11 +1216,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>41_a</t>
+          <t>25_a</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -1229,32 +1229,32 @@
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>2050</v>
+        <v>2045</v>
       </c>
       <c r="H6" t="n">
-        <v>2050</v>
+        <v>2045</v>
       </c>
       <c r="I6" t="n">
-        <v>135.087492546563</v>
+        <v>83.17668254091814</v>
       </c>
       <c r="J6" t="n">
-        <v>135.087492546563</v>
+        <v>83.17668254091814</v>
       </c>
       <c r="K6" t="n">
         <v>100</v>
       </c>
       <c r="L6" t="n">
-        <v>7.685382375769827</v>
+        <v>15.52172525613159</v>
       </c>
       <c r="M6" t="n">
-        <v>7.488092528933219</v>
+        <v>15.49390042686974</v>
       </c>
       <c r="N6" t="n">
         <v>15</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Temperature only</t>
+          <t>Pressure only</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -1272,11 +1272,11 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>25_a</t>
+          <t>58_a</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -1285,32 +1285,32 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>2045</v>
+        <v>2050</v>
       </c>
       <c r="H7" t="n">
-        <v>2045</v>
+        <v>2050</v>
       </c>
       <c r="I7" t="n">
-        <v>83.17668254091814</v>
+        <v>61.78125860955673</v>
       </c>
       <c r="J7" t="n">
-        <v>83.17668254091814</v>
+        <v>61.78125860955673</v>
       </c>
       <c r="K7" t="n">
         <v>100</v>
       </c>
       <c r="L7" t="n">
-        <v>15.52172525613159</v>
+        <v>7.28118475892359</v>
       </c>
       <c r="M7" t="n">
-        <v>15.49390042686974</v>
+        <v>7.375125740250011</v>
       </c>
       <c r="N7" t="n">
         <v>15</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Pressure only</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -1328,11 +1328,11 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>13_b</t>
+          <t>41_a</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -1347,26 +1347,26 @@
         <v>2050</v>
       </c>
       <c r="I8" t="n">
-        <v>72.94993796812167</v>
+        <v>135.087492546563</v>
       </c>
       <c r="J8" t="n">
-        <v>72.94993796812167</v>
+        <v>135.087492546563</v>
       </c>
       <c r="K8" t="n">
         <v>100</v>
       </c>
       <c r="L8" t="n">
-        <v>12.7026408063513</v>
+        <v>7.685382375769827</v>
       </c>
       <c r="M8" t="n">
-        <v>12.20616628491663</v>
+        <v>7.488092528933219</v>
       </c>
       <c r="N8" t="n">
         <v>15</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Temperature only</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>14_a</t>
+          <t>2_b</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1457,25 +1457,25 @@
         <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>2040</v>
+        <v>2045</v>
       </c>
       <c r="H10" t="n">
-        <v>2040</v>
+        <v>2045</v>
       </c>
       <c r="I10" t="n">
-        <v>68.23071827897361</v>
+        <v>72.70748558974221</v>
       </c>
       <c r="J10" t="n">
-        <v>68.23071827897361</v>
+        <v>72.70748558974221</v>
       </c>
       <c r="K10" t="n">
         <v>100</v>
       </c>
       <c r="L10" t="n">
-        <v>14.39816335964983</v>
+        <v>11.52058370585532</v>
       </c>
       <c r="M10" t="n">
-        <v>13.25316015337214</v>
+        <v>11.01168039290185</v>
       </c>
       <c r="N10" t="n">
         <v>15</v>
@@ -1500,11 +1500,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>31_a</t>
+          <t>14_a</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
@@ -1519,26 +1519,26 @@
         <v>2040</v>
       </c>
       <c r="I11" t="n">
-        <v>87.35103979118902</v>
+        <v>68.23071827897361</v>
       </c>
       <c r="J11" t="n">
-        <v>87.35103979118902</v>
+        <v>68.23071827897361</v>
       </c>
       <c r="K11" t="n">
         <v>100</v>
       </c>
       <c r="L11" t="n">
-        <v>18.3022023902338</v>
+        <v>14.39816335964983</v>
       </c>
       <c r="M11" t="n">
-        <v>15.34152481551364</v>
+        <v>13.25316015337214</v>
       </c>
       <c r="N11" t="n">
         <v>15</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Pressure only</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
@@ -1556,11 +1556,11 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2_b</t>
+          <t>31_a</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
@@ -1569,32 +1569,32 @@
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>2045</v>
+        <v>2040</v>
       </c>
       <c r="H12" t="n">
-        <v>2045</v>
+        <v>2040</v>
       </c>
       <c r="I12" t="n">
-        <v>72.70748558974221</v>
+        <v>87.35103979118902</v>
       </c>
       <c r="J12" t="n">
-        <v>72.70748558974221</v>
+        <v>87.35103979118902</v>
       </c>
       <c r="K12" t="n">
         <v>100</v>
       </c>
       <c r="L12" t="n">
-        <v>11.52058370585532</v>
+        <v>18.3022023902338</v>
       </c>
       <c r="M12" t="n">
-        <v>11.01168039290185</v>
+        <v>15.34152481551364</v>
       </c>
       <c r="N12" t="n">
         <v>15</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Pressure only</t>
         </is>
       </c>
       <c r="P12" t="inlineStr"/>
@@ -1612,11 +1612,11 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>41_a</t>
+          <t>13_b</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E13" t="b">
         <v>0</v>
@@ -1625,39 +1625,35 @@
         <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>2030</v>
+        <v>2050</v>
       </c>
       <c r="H13" t="n">
         <v>2050</v>
       </c>
       <c r="I13" t="n">
-        <v>150</v>
+        <v>72.94993796812196</v>
       </c>
       <c r="J13" t="n">
-        <v>150</v>
+        <v>72.94993796812196</v>
       </c>
       <c r="K13" t="n">
         <v>100</v>
       </c>
       <c r="L13" t="n">
-        <v>25</v>
+        <v>12.70264080635227</v>
       </c>
       <c r="M13" t="n">
-        <v>16.07897294360959</v>
+        <v>12.2061662849176</v>
       </c>
       <c r="N13" t="n">
         <v>15</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Temperature only</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Shared-node effect: this pipe is a non-dominant supplier at node 20; without its booster its own pi_dest/theta_dest (168 bar / 16°C) would fall outside the required +/-30 bar / +/-5°C tolerance band around the node's 195 bar / 22°C.</t>
-        </is>
-      </c>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1728,11 +1724,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>13_b</t>
+          <t>41_a</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="E15" t="b">
         <v>0</v>
@@ -1741,35 +1737,39 @@
         <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>2050</v>
+        <v>2030</v>
       </c>
       <c r="H15" t="n">
         <v>2050</v>
       </c>
       <c r="I15" t="n">
-        <v>72.94993796812196</v>
+        <v>150</v>
       </c>
       <c r="J15" t="n">
-        <v>72.94993796812196</v>
+        <v>150</v>
       </c>
       <c r="K15" t="n">
         <v>100</v>
       </c>
       <c r="L15" t="n">
-        <v>12.70264080635227</v>
+        <v>25</v>
       </c>
       <c r="M15" t="n">
-        <v>12.2061662849176</v>
+        <v>16.07897294360959</v>
       </c>
       <c r="N15" t="n">
         <v>15</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr"/>
+          <t>Temperature only</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Shared-node effect: this pipe is a non-dominant supplier at node 20; without its booster its own pi_dest/theta_dest (168 bar / 16°C) would fall outside the required +/-30 bar / +/-5°C tolerance band around the node's 195 bar / 22°C.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>14_a</t>
+          <t>2_b</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1857,25 +1857,25 @@
         <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>2040</v>
+        <v>2045</v>
       </c>
       <c r="H17" t="n">
-        <v>2040</v>
+        <v>2045</v>
       </c>
       <c r="I17" t="n">
-        <v>68.23071827897361</v>
+        <v>72.70748558974221</v>
       </c>
       <c r="J17" t="n">
-        <v>68.23071827897361</v>
+        <v>72.70748558974221</v>
       </c>
       <c r="K17" t="n">
         <v>100</v>
       </c>
       <c r="L17" t="n">
-        <v>14.39816335964983</v>
+        <v>11.52058370585532</v>
       </c>
       <c r="M17" t="n">
-        <v>13.25316015337214</v>
+        <v>11.01168039290185</v>
       </c>
       <c r="N17" t="n">
         <v>15</v>
@@ -1900,11 +1900,11 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>31_a</t>
+          <t>14_a</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E18" t="b">
         <v>0</v>
@@ -1919,26 +1919,26 @@
         <v>2040</v>
       </c>
       <c r="I18" t="n">
-        <v>87.35103979118902</v>
+        <v>68.23071827897361</v>
       </c>
       <c r="J18" t="n">
-        <v>87.35103979118902</v>
+        <v>68.23071827897361</v>
       </c>
       <c r="K18" t="n">
         <v>100</v>
       </c>
       <c r="L18" t="n">
-        <v>18.3022023902338</v>
+        <v>14.39816335964983</v>
       </c>
       <c r="M18" t="n">
-        <v>15.34152481551364</v>
+        <v>13.25316015337214</v>
       </c>
       <c r="N18" t="n">
         <v>15</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Pressure only</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="P18" t="inlineStr"/>
@@ -1956,11 +1956,11 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2_b</t>
+          <t>31_a</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E19" t="b">
         <v>0</v>
@@ -1969,32 +1969,32 @@
         <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>2045</v>
+        <v>2040</v>
       </c>
       <c r="H19" t="n">
-        <v>2045</v>
+        <v>2040</v>
       </c>
       <c r="I19" t="n">
-        <v>72.70748558974221</v>
+        <v>87.35103979118902</v>
       </c>
       <c r="J19" t="n">
-        <v>72.70748558974221</v>
+        <v>87.35103979118902</v>
       </c>
       <c r="K19" t="n">
         <v>100</v>
       </c>
       <c r="L19" t="n">
-        <v>11.52058370585532</v>
+        <v>18.3022023902338</v>
       </c>
       <c r="M19" t="n">
-        <v>11.01168039290185</v>
+        <v>15.34152481551364</v>
       </c>
       <c r="N19" t="n">
         <v>15</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Pressure only</t>
         </is>
       </c>
       <c r="P19" t="inlineStr"/>
@@ -2012,11 +2012,11 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>25_a</t>
+          <t>13_b</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E20" t="b">
         <v>0</v>
@@ -2025,32 +2025,32 @@
         <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>2045</v>
+        <v>2050</v>
       </c>
       <c r="H20" t="n">
-        <v>2045</v>
+        <v>2050</v>
       </c>
       <c r="I20" t="n">
-        <v>83.17668254091814</v>
+        <v>52.60826380850764</v>
       </c>
       <c r="J20" t="n">
-        <v>83.17668254091814</v>
+        <v>52.60826380850764</v>
       </c>
       <c r="K20" t="n">
         <v>100</v>
       </c>
       <c r="L20" t="n">
-        <v>15.52172525613159</v>
+        <v>12.93869871806898</v>
       </c>
       <c r="M20" t="n">
-        <v>15.49390042686974</v>
+        <v>12.44222419663431</v>
       </c>
       <c r="N20" t="n">
         <v>15</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Pressure only</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="P20" t="inlineStr"/>
@@ -2068,11 +2068,11 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>13_b</t>
+          <t>25_a</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E21" t="b">
         <v>0</v>
@@ -2081,32 +2081,32 @@
         <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>2050</v>
+        <v>2045</v>
       </c>
       <c r="H21" t="n">
-        <v>2050</v>
+        <v>2045</v>
       </c>
       <c r="I21" t="n">
-        <v>52.60826380850764</v>
+        <v>83.17668254091814</v>
       </c>
       <c r="J21" t="n">
-        <v>52.60826380850764</v>
+        <v>83.17668254091814</v>
       </c>
       <c r="K21" t="n">
         <v>100</v>
       </c>
       <c r="L21" t="n">
-        <v>12.93869871806898</v>
+        <v>15.52172525613159</v>
       </c>
       <c r="M21" t="n">
-        <v>12.44222419663431</v>
+        <v>15.49390042686974</v>
       </c>
       <c r="N21" t="n">
         <v>15</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Pressure only</t>
         </is>
       </c>
       <c r="P21" t="inlineStr"/>
@@ -2124,7 +2124,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>14_a</t>
+          <t>2_b</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -2137,25 +2137,25 @@
         <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>2045</v>
+        <v>2035</v>
       </c>
       <c r="H22" t="n">
-        <v>2045</v>
+        <v>2035</v>
       </c>
       <c r="I22" t="n">
-        <v>68.23071827897361</v>
+        <v>72.70748558974221</v>
       </c>
       <c r="J22" t="n">
-        <v>68.23071827897361</v>
+        <v>72.70748558974221</v>
       </c>
       <c r="K22" t="n">
         <v>100</v>
       </c>
       <c r="L22" t="n">
-        <v>14.39816335964983</v>
+        <v>11.52058370585532</v>
       </c>
       <c r="M22" t="n">
-        <v>13.25316015337214</v>
+        <v>11.01168039290185</v>
       </c>
       <c r="N22" t="n">
         <v>15</v>
@@ -2180,11 +2180,11 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>31_a</t>
+          <t>14_a</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E23" t="b">
         <v>0</v>
@@ -2193,32 +2193,32 @@
         <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>2050</v>
+        <v>2045</v>
       </c>
       <c r="H23" t="n">
-        <v>2050</v>
+        <v>2045</v>
       </c>
       <c r="I23" t="n">
-        <v>87.35103979118902</v>
+        <v>68.23071827897361</v>
       </c>
       <c r="J23" t="n">
-        <v>87.35103979118902</v>
+        <v>68.23071827897361</v>
       </c>
       <c r="K23" t="n">
         <v>100</v>
       </c>
       <c r="L23" t="n">
-        <v>18.3022023902338</v>
+        <v>14.39816335964983</v>
       </c>
       <c r="M23" t="n">
-        <v>15.34152481551364</v>
+        <v>13.25316015337214</v>
       </c>
       <c r="N23" t="n">
         <v>15</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Pressure only</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="P23" t="inlineStr"/>
@@ -2236,11 +2236,11 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2_b</t>
+          <t>31_a</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E24" t="b">
         <v>0</v>
@@ -2249,32 +2249,32 @@
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>2035</v>
+        <v>2050</v>
       </c>
       <c r="H24" t="n">
-        <v>2035</v>
+        <v>2050</v>
       </c>
       <c r="I24" t="n">
-        <v>72.70748558974221</v>
+        <v>87.35103979118902</v>
       </c>
       <c r="J24" t="n">
-        <v>72.70748558974221</v>
+        <v>87.35103979118902</v>
       </c>
       <c r="K24" t="n">
         <v>100</v>
       </c>
       <c r="L24" t="n">
-        <v>11.52058370585532</v>
+        <v>18.3022023902338</v>
       </c>
       <c r="M24" t="n">
-        <v>11.01168039290185</v>
+        <v>15.34152481551364</v>
       </c>
       <c r="N24" t="n">
         <v>15</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Pressure only</t>
         </is>
       </c>
       <c r="P24" t="inlineStr"/>
@@ -2292,11 +2292,11 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>25_a</t>
+          <t>13_b</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E25" t="b">
         <v>0</v>
@@ -2305,32 +2305,32 @@
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>2040</v>
+        <v>2050</v>
       </c>
       <c r="H25" t="n">
-        <v>2040</v>
+        <v>2050</v>
       </c>
       <c r="I25" t="n">
-        <v>83.17668254091814</v>
+        <v>52.60826380850764</v>
       </c>
       <c r="J25" t="n">
-        <v>83.17668254091814</v>
+        <v>52.60826380850764</v>
       </c>
       <c r="K25" t="n">
         <v>100</v>
       </c>
       <c r="L25" t="n">
-        <v>15.52172525613159</v>
+        <v>12.93869871806898</v>
       </c>
       <c r="M25" t="n">
-        <v>15.49390042686974</v>
+        <v>12.44222419663431</v>
       </c>
       <c r="N25" t="n">
         <v>15</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Pressure only</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="P25" t="inlineStr"/>
@@ -2348,11 +2348,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>13_b</t>
+          <t>25_a</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E26" t="b">
         <v>0</v>
@@ -2361,32 +2361,32 @@
         <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="H26" t="n">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="I26" t="n">
-        <v>52.60826380850764</v>
+        <v>83.17668254091814</v>
       </c>
       <c r="J26" t="n">
-        <v>52.60826380850764</v>
+        <v>83.17668254091814</v>
       </c>
       <c r="K26" t="n">
         <v>100</v>
       </c>
       <c r="L26" t="n">
-        <v>12.93869871806898</v>
+        <v>15.52172525613159</v>
       </c>
       <c r="M26" t="n">
-        <v>12.44222419663431</v>
+        <v>15.49390042686974</v>
       </c>
       <c r="N26" t="n">
         <v>15</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Pressure only</t>
         </is>
       </c>
       <c r="P26" t="inlineStr"/>
@@ -2464,7 +2464,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>14_a</t>
+          <t>2_b</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -2477,25 +2477,25 @@
         <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>2040</v>
+        <v>2045</v>
       </c>
       <c r="H28" t="n">
-        <v>2040</v>
+        <v>2045</v>
       </c>
       <c r="I28" t="n">
-        <v>68.23071827897361</v>
+        <v>72.70748558974221</v>
       </c>
       <c r="J28" t="n">
-        <v>68.23071827897361</v>
+        <v>72.70748558974221</v>
       </c>
       <c r="K28" t="n">
         <v>100</v>
       </c>
       <c r="L28" t="n">
-        <v>14.39816335964983</v>
+        <v>11.52058370585532</v>
       </c>
       <c r="M28" t="n">
-        <v>13.25316015337214</v>
+        <v>11.01168039290185</v>
       </c>
       <c r="N28" t="n">
         <v>15</v>
@@ -2520,11 +2520,11 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>31_a</t>
+          <t>14_a</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E29" t="b">
         <v>0</v>
@@ -2539,26 +2539,26 @@
         <v>2040</v>
       </c>
       <c r="I29" t="n">
-        <v>87.35103979118902</v>
+        <v>68.23071827897361</v>
       </c>
       <c r="J29" t="n">
-        <v>87.35103979118902</v>
+        <v>68.23071827897361</v>
       </c>
       <c r="K29" t="n">
         <v>100</v>
       </c>
       <c r="L29" t="n">
-        <v>18.3022023902338</v>
+        <v>14.39816335964983</v>
       </c>
       <c r="M29" t="n">
-        <v>15.34152481551364</v>
+        <v>13.25316015337214</v>
       </c>
       <c r="N29" t="n">
         <v>15</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Pressure only</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="P29" t="inlineStr"/>
@@ -2576,11 +2576,11 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2_b</t>
+          <t>31_a</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E30" t="b">
         <v>0</v>
@@ -2589,32 +2589,32 @@
         <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>2045</v>
+        <v>2040</v>
       </c>
       <c r="H30" t="n">
-        <v>2045</v>
+        <v>2040</v>
       </c>
       <c r="I30" t="n">
-        <v>72.70748558974221</v>
+        <v>87.35103979118902</v>
       </c>
       <c r="J30" t="n">
-        <v>72.70748558974221</v>
+        <v>87.35103979118902</v>
       </c>
       <c r="K30" t="n">
         <v>100</v>
       </c>
       <c r="L30" t="n">
-        <v>11.52058370585532</v>
+        <v>18.3022023902338</v>
       </c>
       <c r="M30" t="n">
-        <v>11.01168039290185</v>
+        <v>15.34152481551364</v>
       </c>
       <c r="N30" t="n">
         <v>15</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Pressure only</t>
         </is>
       </c>
       <c r="P30" t="inlineStr"/>
@@ -2632,11 +2632,11 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>41_a</t>
+          <t>13_b</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="E31" t="b">
         <v>0</v>
@@ -2651,26 +2651,26 @@
         <v>2050</v>
       </c>
       <c r="I31" t="n">
-        <v>135.087492546563</v>
+        <v>72.94993796812295</v>
       </c>
       <c r="J31" t="n">
-        <v>135.087492546563</v>
+        <v>72.94993796812295</v>
       </c>
       <c r="K31" t="n">
         <v>100</v>
       </c>
       <c r="L31" t="n">
-        <v>7.685382375769827</v>
+        <v>12.70264080635081</v>
       </c>
       <c r="M31" t="n">
-        <v>7.488092528933219</v>
+        <v>12.20616628491614</v>
       </c>
       <c r="N31" t="n">
         <v>15</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Temperature only</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="P31" t="inlineStr"/>
@@ -2744,11 +2744,11 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>13_b</t>
+          <t>41_a</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="E33" t="b">
         <v>0</v>
@@ -2763,26 +2763,26 @@
         <v>2050</v>
       </c>
       <c r="I33" t="n">
-        <v>72.94993796812295</v>
+        <v>135.087492546563</v>
       </c>
       <c r="J33" t="n">
-        <v>72.94993796812295</v>
+        <v>135.087492546563</v>
       </c>
       <c r="K33" t="n">
         <v>100</v>
       </c>
       <c r="L33" t="n">
-        <v>12.70264080635081</v>
+        <v>7.685382375769827</v>
       </c>
       <c r="M33" t="n">
-        <v>12.20616628491614</v>
+        <v>7.488092528933219</v>
       </c>
       <c r="N33" t="n">
         <v>15</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Temperature only</t>
         </is>
       </c>
       <c r="P33" t="inlineStr"/>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>14_a</t>
+          <t>2_b</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -2873,25 +2873,25 @@
         <v>1</v>
       </c>
       <c r="G35" t="n">
-        <v>2035</v>
+        <v>2045</v>
       </c>
       <c r="H35" t="n">
-        <v>2035</v>
+        <v>2045</v>
       </c>
       <c r="I35" t="n">
-        <v>68.23071827897361</v>
+        <v>72.70748558974221</v>
       </c>
       <c r="J35" t="n">
-        <v>68.23071827897361</v>
+        <v>72.70748558974221</v>
       </c>
       <c r="K35" t="n">
         <v>100</v>
       </c>
       <c r="L35" t="n">
-        <v>14.39816335964983</v>
+        <v>11.52058370585532</v>
       </c>
       <c r="M35" t="n">
-        <v>13.25316015337214</v>
+        <v>11.01168039290185</v>
       </c>
       <c r="N35" t="n">
         <v>15</v>
@@ -2916,11 +2916,11 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>31_a</t>
+          <t>14_a</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E36" t="b">
         <v>0</v>
@@ -2929,32 +2929,32 @@
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>2050</v>
+        <v>2035</v>
       </c>
       <c r="H36" t="n">
-        <v>2050</v>
+        <v>2035</v>
       </c>
       <c r="I36" t="n">
-        <v>87.35103979118902</v>
+        <v>68.23071827897361</v>
       </c>
       <c r="J36" t="n">
-        <v>87.35103979118902</v>
+        <v>68.23071827897361</v>
       </c>
       <c r="K36" t="n">
         <v>100</v>
       </c>
       <c r="L36" t="n">
-        <v>18.3022023902338</v>
+        <v>14.39816335964983</v>
       </c>
       <c r="M36" t="n">
-        <v>15.34152481551364</v>
+        <v>13.25316015337214</v>
       </c>
       <c r="N36" t="n">
         <v>15</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Pressure only</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="P36" t="inlineStr"/>
@@ -2972,11 +2972,11 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2_b</t>
+          <t>31_a</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E37" t="b">
         <v>0</v>
@@ -2985,32 +2985,32 @@
         <v>1</v>
       </c>
       <c r="G37" t="n">
-        <v>2045</v>
+        <v>2050</v>
       </c>
       <c r="H37" t="n">
-        <v>2045</v>
+        <v>2050</v>
       </c>
       <c r="I37" t="n">
-        <v>72.70748558974221</v>
+        <v>87.35103979118902</v>
       </c>
       <c r="J37" t="n">
-        <v>72.70748558974221</v>
+        <v>87.35103979118902</v>
       </c>
       <c r="K37" t="n">
         <v>100</v>
       </c>
       <c r="L37" t="n">
-        <v>11.52058370585532</v>
+        <v>18.3022023902338</v>
       </c>
       <c r="M37" t="n">
-        <v>11.01168039290185</v>
+        <v>15.34152481551364</v>
       </c>
       <c r="N37" t="n">
         <v>15</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Pressure only</t>
         </is>
       </c>
       <c r="P37" t="inlineStr"/>
@@ -3028,11 +3028,11 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>25_a</t>
+          <t>13_b</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E38" t="b">
         <v>0</v>
@@ -3041,32 +3041,32 @@
         <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>2045</v>
+        <v>2050</v>
       </c>
       <c r="H38" t="n">
-        <v>2045</v>
+        <v>2050</v>
       </c>
       <c r="I38" t="n">
-        <v>83.17668254091814</v>
+        <v>72.9499379681217</v>
       </c>
       <c r="J38" t="n">
-        <v>83.17668254091814</v>
+        <v>72.9499379681217</v>
       </c>
       <c r="K38" t="n">
         <v>100</v>
       </c>
       <c r="L38" t="n">
-        <v>15.52172525613159</v>
+        <v>12.70264080635134</v>
       </c>
       <c r="M38" t="n">
-        <v>15.49390042686974</v>
+        <v>12.20616628491667</v>
       </c>
       <c r="N38" t="n">
         <v>15</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Pressure only</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="P38" t="inlineStr"/>
@@ -3084,11 +3084,11 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>13_b</t>
+          <t>25_a</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E39" t="b">
         <v>0</v>
@@ -3097,32 +3097,32 @@
         <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>2050</v>
+        <v>2045</v>
       </c>
       <c r="H39" t="n">
-        <v>2050</v>
+        <v>2045</v>
       </c>
       <c r="I39" t="n">
-        <v>72.9499379681217</v>
+        <v>83.17668254091814</v>
       </c>
       <c r="J39" t="n">
-        <v>72.9499379681217</v>
+        <v>83.17668254091814</v>
       </c>
       <c r="K39" t="n">
         <v>100</v>
       </c>
       <c r="L39" t="n">
-        <v>12.70264080635134</v>
+        <v>15.52172525613159</v>
       </c>
       <c r="M39" t="n">
-        <v>12.20616628491667</v>
+        <v>15.49390042686974</v>
       </c>
       <c r="N39" t="n">
         <v>15</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Pressure only</t>
         </is>
       </c>
       <c r="P39" t="inlineStr"/>
@@ -3200,7 +3200,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>14_a</t>
+          <t>2_b</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -3213,25 +3213,25 @@
         <v>1</v>
       </c>
       <c r="G41" t="n">
-        <v>2040</v>
+        <v>2045</v>
       </c>
       <c r="H41" t="n">
-        <v>2040</v>
+        <v>2045</v>
       </c>
       <c r="I41" t="n">
-        <v>68.23071827897361</v>
+        <v>72.70748558974221</v>
       </c>
       <c r="J41" t="n">
-        <v>68.23071827897361</v>
+        <v>72.70748558974221</v>
       </c>
       <c r="K41" t="n">
         <v>100</v>
       </c>
       <c r="L41" t="n">
-        <v>14.39816335964983</v>
+        <v>11.52058370585532</v>
       </c>
       <c r="M41" t="n">
-        <v>13.25316015337214</v>
+        <v>11.01168039290185</v>
       </c>
       <c r="N41" t="n">
         <v>15</v>
@@ -3256,11 +3256,11 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>31_a</t>
+          <t>14_a</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E42" t="b">
         <v>0</v>
@@ -3269,32 +3269,32 @@
         <v>1</v>
       </c>
       <c r="G42" t="n">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="H42" t="n">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="I42" t="n">
-        <v>87.35103979118902</v>
+        <v>68.23071827897361</v>
       </c>
       <c r="J42" t="n">
-        <v>87.35103979118902</v>
+        <v>68.23071827897361</v>
       </c>
       <c r="K42" t="n">
         <v>100</v>
       </c>
       <c r="L42" t="n">
-        <v>18.3022023902338</v>
+        <v>14.39816335964983</v>
       </c>
       <c r="M42" t="n">
-        <v>15.34152481551364</v>
+        <v>13.25316015337214</v>
       </c>
       <c r="N42" t="n">
         <v>15</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Pressure only</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="P42" t="inlineStr"/>
@@ -3312,11 +3312,11 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2_b</t>
+          <t>31_a</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E43" t="b">
         <v>0</v>
@@ -3325,32 +3325,32 @@
         <v>1</v>
       </c>
       <c r="G43" t="n">
-        <v>2045</v>
+        <v>2050</v>
       </c>
       <c r="H43" t="n">
-        <v>2045</v>
+        <v>2050</v>
       </c>
       <c r="I43" t="n">
-        <v>72.70748558974221</v>
+        <v>87.35103979118902</v>
       </c>
       <c r="J43" t="n">
-        <v>72.70748558974221</v>
+        <v>87.35103979118902</v>
       </c>
       <c r="K43" t="n">
         <v>100</v>
       </c>
       <c r="L43" t="n">
-        <v>11.52058370585532</v>
+        <v>18.3022023902338</v>
       </c>
       <c r="M43" t="n">
-        <v>11.01168039290185</v>
+        <v>15.34152481551364</v>
       </c>
       <c r="N43" t="n">
         <v>15</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Pressure only</t>
         </is>
       </c>
       <c r="P43" t="inlineStr"/>
@@ -3368,11 +3368,11 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>41_a</t>
+          <t>13_b</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E44" t="b">
         <v>0</v>
@@ -3381,39 +3381,35 @@
         <v>1</v>
       </c>
       <c r="G44" t="n">
-        <v>2030</v>
+        <v>2050</v>
       </c>
       <c r="H44" t="n">
         <v>2050</v>
       </c>
       <c r="I44" t="n">
-        <v>150</v>
+        <v>72.94993796812173</v>
       </c>
       <c r="J44" t="n">
-        <v>150</v>
+        <v>72.94993796812173</v>
       </c>
       <c r="K44" t="n">
         <v>100</v>
       </c>
       <c r="L44" t="n">
-        <v>25</v>
+        <v>12.70264080635134</v>
       </c>
       <c r="M44" t="n">
-        <v>16.07897294360959</v>
+        <v>12.20616628491667</v>
       </c>
       <c r="N44" t="n">
         <v>15</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Temperature only</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>Shared-node effect: this pipe is a non-dominant supplier at node 20; without its booster its own pi_dest/theta_dest (168 bar / 16°C) would fall outside the required +/-30 bar / +/-5°C tolerance band around the node's 195 bar / 22°C.</t>
-        </is>
-      </c>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3484,11 +3480,11 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>13_b</t>
+          <t>41_a</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="E46" t="b">
         <v>0</v>
@@ -3497,35 +3493,39 @@
         <v>1</v>
       </c>
       <c r="G46" t="n">
-        <v>2050</v>
+        <v>2030</v>
       </c>
       <c r="H46" t="n">
         <v>2050</v>
       </c>
       <c r="I46" t="n">
-        <v>72.94993796812173</v>
+        <v>150</v>
       </c>
       <c r="J46" t="n">
-        <v>72.94993796812173</v>
+        <v>150</v>
       </c>
       <c r="K46" t="n">
         <v>100</v>
       </c>
       <c r="L46" t="n">
-        <v>12.70264080635134</v>
+        <v>25</v>
       </c>
       <c r="M46" t="n">
-        <v>12.20616628491667</v>
+        <v>16.07897294360959</v>
       </c>
       <c r="N46" t="n">
         <v>15</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr"/>
+          <t>Temperature only</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Shared-node effect: this pipe is a non-dominant supplier at node 20; without its booster its own pi_dest/theta_dest (168 bar / 16°C) would fall outside the required +/-30 bar / +/-5°C tolerance band around the node's 195 bar / 22°C.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3600,11 +3600,11 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>14_a</t>
+          <t>2_b</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="E48" t="b">
         <v>0</v>
@@ -3613,25 +3613,25 @@
         <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>2040</v>
+        <v>2045</v>
       </c>
       <c r="H48" t="n">
-        <v>2040</v>
+        <v>2045</v>
       </c>
       <c r="I48" t="n">
-        <v>76.97104401094329</v>
+        <v>87.93509768253111</v>
       </c>
       <c r="J48" t="n">
-        <v>76.97104401094329</v>
+        <v>87.93509768253111</v>
       </c>
       <c r="K48" t="n">
         <v>100</v>
       </c>
       <c r="L48" t="n">
-        <v>25.4791129998713</v>
+        <v>23.19354690367037</v>
       </c>
       <c r="M48" t="n">
-        <v>23.53838500964068</v>
+        <v>22.45514163646351</v>
       </c>
       <c r="N48" t="n">
         <v>32</v>
@@ -3656,45 +3656,45 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>31_a</t>
+          <t>14_a</t>
         </is>
       </c>
       <c r="D49" t="n">
         <v>30</v>
       </c>
       <c r="E49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
         <v>1</v>
       </c>
       <c r="G49" t="n">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="H49" t="n">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="I49" t="n">
-        <v>96.01490431867812</v>
+        <v>76.97104401094329</v>
       </c>
       <c r="J49" t="n">
-        <v>96.01490431867812</v>
+        <v>76.97104401094329</v>
       </c>
       <c r="K49" t="n">
         <v>100</v>
       </c>
       <c r="L49" t="n">
-        <v>36.28255339045213</v>
+        <v>25.4791129998713</v>
       </c>
       <c r="M49" t="n">
-        <v>36.6839072972405</v>
+        <v>23.53838500964068</v>
       </c>
       <c r="N49" t="n">
         <v>32</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Pressure only</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="P49" t="inlineStr"/>
@@ -3712,45 +3712,45 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2_b</t>
+          <t>31_a</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="E50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F50" t="n">
         <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>2045</v>
+        <v>2050</v>
       </c>
       <c r="H50" t="n">
-        <v>2045</v>
+        <v>2050</v>
       </c>
       <c r="I50" t="n">
-        <v>87.93509768253111</v>
+        <v>96.01490431867812</v>
       </c>
       <c r="J50" t="n">
-        <v>87.93509768253111</v>
+        <v>96.01490431867812</v>
       </c>
       <c r="K50" t="n">
         <v>100</v>
       </c>
       <c r="L50" t="n">
-        <v>23.19354690367037</v>
+        <v>36.28255339045213</v>
       </c>
       <c r="M50" t="n">
-        <v>22.45514163646351</v>
+        <v>36.6839072972405</v>
       </c>
       <c r="N50" t="n">
         <v>32</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Pressure only</t>
         </is>
       </c>
       <c r="P50" t="inlineStr"/>
@@ -3768,11 +3768,11 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>25_a</t>
+          <t>13_b</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E51" t="b">
         <v>0</v>
@@ -3781,25 +3781,25 @@
         <v>1</v>
       </c>
       <c r="G51" t="n">
-        <v>2045</v>
+        <v>2050</v>
       </c>
       <c r="H51" t="n">
-        <v>2045</v>
+        <v>2050</v>
       </c>
       <c r="I51" t="n">
-        <v>87.38150101973842</v>
+        <v>65.09457797059355</v>
       </c>
       <c r="J51" t="n">
-        <v>87.38150101973842</v>
+        <v>65.09457797059355</v>
       </c>
       <c r="K51" t="n">
         <v>100</v>
       </c>
       <c r="L51" t="n">
-        <v>27.09593705181401</v>
+        <v>24.63421202281581</v>
       </c>
       <c r="M51" t="n">
-        <v>27.12370763736967</v>
+        <v>24.48554738510013</v>
       </c>
       <c r="N51" t="n">
         <v>32</v>
@@ -3824,11 +3824,11 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>13_b</t>
+          <t>25_a</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E52" t="b">
         <v>0</v>
@@ -3837,25 +3837,25 @@
         <v>1</v>
       </c>
       <c r="G52" t="n">
-        <v>2050</v>
+        <v>2045</v>
       </c>
       <c r="H52" t="n">
-        <v>2050</v>
+        <v>2045</v>
       </c>
       <c r="I52" t="n">
-        <v>65.09457797059355</v>
+        <v>87.38150101973842</v>
       </c>
       <c r="J52" t="n">
-        <v>65.09457797059355</v>
+        <v>87.38150101973842</v>
       </c>
       <c r="K52" t="n">
         <v>100</v>
       </c>
       <c r="L52" t="n">
-        <v>24.63421202281581</v>
+        <v>27.09593705181401</v>
       </c>
       <c r="M52" t="n">
-        <v>24.48554738510013</v>
+        <v>27.12370763736967</v>
       </c>
       <c r="N52" t="n">
         <v>32</v>
@@ -3940,11 +3940,11 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>14_a</t>
+          <t>2_b</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="E54" t="b">
         <v>0</v>
@@ -3953,25 +3953,25 @@
         <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>2030</v>
+        <v>2045</v>
       </c>
       <c r="H54" t="n">
-        <v>2030</v>
+        <v>2045</v>
       </c>
       <c r="I54" t="n">
-        <v>76.97104401094329</v>
+        <v>87.93509768253111</v>
       </c>
       <c r="J54" t="n">
-        <v>76.97104401094329</v>
+        <v>87.93509768253111</v>
       </c>
       <c r="K54" t="n">
         <v>100</v>
       </c>
       <c r="L54" t="n">
-        <v>25.4791129998713</v>
+        <v>23.19354690367037</v>
       </c>
       <c r="M54" t="n">
-        <v>23.53838500964068</v>
+        <v>22.45514163646351</v>
       </c>
       <c r="N54" t="n">
         <v>32</v>
@@ -3996,7 +3996,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>31_a</t>
+          <t>14_a</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -4009,25 +4009,25 @@
         <v>1</v>
       </c>
       <c r="G55" t="n">
-        <v>2040</v>
+        <v>2030</v>
       </c>
       <c r="H55" t="n">
-        <v>2040</v>
+        <v>2030</v>
       </c>
       <c r="I55" t="n">
-        <v>94.08777135878756</v>
+        <v>76.97104401094329</v>
       </c>
       <c r="J55" t="n">
-        <v>94.08777135878756</v>
+        <v>76.97104401094329</v>
       </c>
       <c r="K55" t="n">
         <v>100</v>
       </c>
       <c r="L55" t="n">
-        <v>32.08262364503698</v>
+        <v>25.4791129998713</v>
       </c>
       <c r="M55" t="n">
-        <v>26.10570821868824</v>
+        <v>23.53838500964068</v>
       </c>
       <c r="N55" t="n">
         <v>32</v>
@@ -4052,14 +4052,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>65_b</t>
+          <t>54_a</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="E56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>1</v>
@@ -4071,26 +4071,26 @@
         <v>2050</v>
       </c>
       <c r="I56" t="n">
-        <v>62.29813296627455</v>
+        <v>144.3664028948996</v>
       </c>
       <c r="J56" t="n">
-        <v>62.29813296627455</v>
+        <v>143.6069409160063</v>
       </c>
       <c r="K56" t="n">
         <v>100</v>
       </c>
       <c r="L56" t="n">
-        <v>26.76040136691488</v>
+        <v>26.71025928518643</v>
       </c>
       <c r="M56" t="n">
-        <v>22.34896224971083</v>
+        <v>26.80997492935868</v>
       </c>
       <c r="N56" t="n">
         <v>32</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Temperature only</t>
         </is>
       </c>
       <c r="P56" t="inlineStr"/>
@@ -4108,11 +4108,11 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2_b</t>
+          <t>31_a</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="E57" t="b">
         <v>0</v>
@@ -4121,25 +4121,25 @@
         <v>1</v>
       </c>
       <c r="G57" t="n">
-        <v>2045</v>
+        <v>2040</v>
       </c>
       <c r="H57" t="n">
-        <v>2045</v>
+        <v>2040</v>
       </c>
       <c r="I57" t="n">
-        <v>87.93509768253111</v>
+        <v>94.08777135878756</v>
       </c>
       <c r="J57" t="n">
-        <v>87.93509768253111</v>
+        <v>94.08777135878756</v>
       </c>
       <c r="K57" t="n">
         <v>100</v>
       </c>
       <c r="L57" t="n">
-        <v>23.19354690367037</v>
+        <v>32.08262364503698</v>
       </c>
       <c r="M57" t="n">
-        <v>22.45514163646351</v>
+        <v>26.10570821868824</v>
       </c>
       <c r="N57" t="n">
         <v>32</v>
@@ -4164,11 +4164,11 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>60_b</t>
+          <t>61_a</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E58" t="b">
         <v>1</v>
@@ -4177,25 +4177,25 @@
         <v>1</v>
       </c>
       <c r="G58" t="n">
-        <v>2035</v>
+        <v>2050</v>
       </c>
       <c r="H58" t="n">
-        <v>2035</v>
+        <v>2050</v>
       </c>
       <c r="I58" t="n">
-        <v>90.69294174229272</v>
+        <v>73.27503741519905</v>
       </c>
       <c r="J58" t="n">
-        <v>90.69294174229272</v>
+        <v>73.27503741519905</v>
       </c>
       <c r="K58" t="n">
         <v>100</v>
       </c>
       <c r="L58" t="n">
-        <v>24.46339143641816</v>
+        <v>26.80692855889654</v>
       </c>
       <c r="M58" t="n">
-        <v>22.22858476072506</v>
+        <v>27.5098033169456</v>
       </c>
       <c r="N58" t="n">
         <v>32</v>
@@ -4220,11 +4220,11 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>25_a</t>
+          <t>65_b</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E59" t="b">
         <v>0</v>
@@ -4233,25 +4233,25 @@
         <v>1</v>
       </c>
       <c r="G59" t="n">
-        <v>2045</v>
+        <v>2050</v>
       </c>
       <c r="H59" t="n">
-        <v>2045</v>
+        <v>2050</v>
       </c>
       <c r="I59" t="n">
-        <v>87.38150101973842</v>
+        <v>62.29813296627455</v>
       </c>
       <c r="J59" t="n">
-        <v>87.38150101973842</v>
+        <v>62.29813296627455</v>
       </c>
       <c r="K59" t="n">
         <v>100</v>
       </c>
       <c r="L59" t="n">
-        <v>27.09593705181401</v>
+        <v>26.76040136691488</v>
       </c>
       <c r="M59" t="n">
-        <v>27.12370763736967</v>
+        <v>22.34896224971083</v>
       </c>
       <c r="N59" t="n">
         <v>32</v>
@@ -4276,38 +4276,38 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>61_a</t>
+          <t>25_a</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="E60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F60" t="n">
         <v>1</v>
       </c>
       <c r="G60" t="n">
-        <v>2050</v>
+        <v>2045</v>
       </c>
       <c r="H60" t="n">
-        <v>2050</v>
+        <v>2045</v>
       </c>
       <c r="I60" t="n">
-        <v>73.27503741519905</v>
+        <v>87.38150101973842</v>
       </c>
       <c r="J60" t="n">
-        <v>73.27503741519905</v>
+        <v>87.38150101973842</v>
       </c>
       <c r="K60" t="n">
         <v>100</v>
       </c>
       <c r="L60" t="n">
-        <v>26.80692855889654</v>
+        <v>27.09593705181401</v>
       </c>
       <c r="M60" t="n">
-        <v>27.5098033169456</v>
+        <v>27.12370763736967</v>
       </c>
       <c r="N60" t="n">
         <v>32</v>
@@ -4332,45 +4332,45 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>10_a</t>
+          <t>60_b</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F61" t="n">
         <v>1</v>
       </c>
       <c r="G61" t="n">
-        <v>2030</v>
+        <v>2035</v>
       </c>
       <c r="H61" t="n">
-        <v>2030</v>
+        <v>2035</v>
       </c>
       <c r="I61" t="n">
-        <v>123.1245526439649</v>
+        <v>90.69294174229272</v>
       </c>
       <c r="J61" t="n">
-        <v>122.869494826188</v>
+        <v>90.69294174229272</v>
       </c>
       <c r="K61" t="n">
         <v>100</v>
       </c>
       <c r="L61" t="n">
-        <v>23.21269847782931</v>
+        <v>24.46339143641816</v>
       </c>
       <c r="M61" t="n">
-        <v>23.46148378669019</v>
+        <v>22.22858476072506</v>
       </c>
       <c r="N61" t="n">
         <v>32</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Temperature only</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="P61" t="inlineStr"/>
@@ -4388,38 +4388,38 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>54_a</t>
+          <t>10_a</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E62" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F62" t="n">
         <v>1</v>
       </c>
       <c r="G62" t="n">
-        <v>2050</v>
+        <v>2030</v>
       </c>
       <c r="H62" t="n">
-        <v>2050</v>
+        <v>2030</v>
       </c>
       <c r="I62" t="n">
-        <v>144.3664028948996</v>
+        <v>123.1245526439649</v>
       </c>
       <c r="J62" t="n">
-        <v>143.6069409160063</v>
+        <v>122.869494826188</v>
       </c>
       <c r="K62" t="n">
         <v>100</v>
       </c>
       <c r="L62" t="n">
-        <v>26.71025928518643</v>
+        <v>23.21269847782931</v>
       </c>
       <c r="M62" t="n">
-        <v>26.80997492935868</v>
+        <v>23.46148378669019</v>
       </c>
       <c r="N62" t="n">
         <v>32</v>
@@ -4444,7 +4444,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>14_a</t>
+          <t>2_b</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -4457,25 +4457,25 @@
         <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>2030</v>
+        <v>2045</v>
       </c>
       <c r="H63" t="n">
-        <v>2030</v>
+        <v>2045</v>
       </c>
       <c r="I63" t="n">
-        <v>78.24018961694998</v>
+        <v>76.39458196087037</v>
       </c>
       <c r="J63" t="n">
-        <v>78.24018961694998</v>
+        <v>76.39458196087037</v>
       </c>
       <c r="K63" t="n">
         <v>100</v>
       </c>
       <c r="L63" t="n">
-        <v>32.33945620699593</v>
+        <v>29.55171992167623</v>
       </c>
       <c r="M63" t="n">
-        <v>31.64011030605105</v>
+        <v>28.95222400973573</v>
       </c>
       <c r="N63" t="n">
         <v>32</v>
@@ -4500,11 +4500,11 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>31_a</t>
+          <t>14_a</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E64" t="b">
         <v>1</v>
@@ -4513,32 +4513,32 @@
         <v>1</v>
       </c>
       <c r="G64" t="n">
-        <v>2050</v>
+        <v>2030</v>
       </c>
       <c r="H64" t="n">
-        <v>2050</v>
+        <v>2030</v>
       </c>
       <c r="I64" t="n">
-        <v>96.01490431867812</v>
+        <v>78.24018961694998</v>
       </c>
       <c r="J64" t="n">
-        <v>96.01490431867812</v>
+        <v>78.24018961694998</v>
       </c>
       <c r="K64" t="n">
         <v>100</v>
       </c>
       <c r="L64" t="n">
-        <v>36.28255339045213</v>
+        <v>32.33945620699593</v>
       </c>
       <c r="M64" t="n">
-        <v>36.6839072972405</v>
+        <v>31.64011030605105</v>
       </c>
       <c r="N64" t="n">
         <v>32</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Pressure only</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="P64" t="inlineStr"/>
@@ -4556,11 +4556,11 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2_b</t>
+          <t>31_a</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E65" t="b">
         <v>1</v>
@@ -4569,32 +4569,32 @@
         <v>1</v>
       </c>
       <c r="G65" t="n">
-        <v>2045</v>
+        <v>2050</v>
       </c>
       <c r="H65" t="n">
-        <v>2045</v>
+        <v>2050</v>
       </c>
       <c r="I65" t="n">
-        <v>76.39458196087037</v>
+        <v>96.01490431867812</v>
       </c>
       <c r="J65" t="n">
-        <v>76.39458196087037</v>
+        <v>96.01490431867812</v>
       </c>
       <c r="K65" t="n">
         <v>100</v>
       </c>
       <c r="L65" t="n">
-        <v>29.55171992167623</v>
+        <v>36.28255339045213</v>
       </c>
       <c r="M65" t="n">
-        <v>28.95222400973573</v>
+        <v>36.6839072972405</v>
       </c>
       <c r="N65" t="n">
         <v>32</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Pressure only</t>
         </is>
       </c>
       <c r="P65" t="inlineStr"/>
@@ -4612,11 +4612,11 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>25_a</t>
+          <t>13_b</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E66" t="b">
         <v>0</v>
@@ -4625,25 +4625,25 @@
         <v>1</v>
       </c>
       <c r="G66" t="n">
-        <v>2045</v>
+        <v>2050</v>
       </c>
       <c r="H66" t="n">
-        <v>2045</v>
+        <v>2050</v>
       </c>
       <c r="I66" t="n">
-        <v>87.38150101973842</v>
+        <v>84.59563676007875</v>
       </c>
       <c r="J66" t="n">
-        <v>87.38150101973842</v>
+        <v>84.59563676007875</v>
       </c>
       <c r="K66" t="n">
         <v>100</v>
       </c>
       <c r="L66" t="n">
-        <v>27.09593705181401</v>
+        <v>25.44242266257267</v>
       </c>
       <c r="M66" t="n">
-        <v>27.12370763736967</v>
+        <v>25.29375802485699</v>
       </c>
       <c r="N66" t="n">
         <v>32</v>
@@ -4668,11 +4668,11 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>13_b</t>
+          <t>25_a</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E67" t="b">
         <v>0</v>
@@ -4681,25 +4681,25 @@
         <v>1</v>
       </c>
       <c r="G67" t="n">
-        <v>2050</v>
+        <v>2045</v>
       </c>
       <c r="H67" t="n">
-        <v>2050</v>
+        <v>2045</v>
       </c>
       <c r="I67" t="n">
-        <v>84.59563676007875</v>
+        <v>87.38150101973842</v>
       </c>
       <c r="J67" t="n">
-        <v>84.59563676007875</v>
+        <v>87.38150101973842</v>
       </c>
       <c r="K67" t="n">
         <v>100</v>
       </c>
       <c r="L67" t="n">
-        <v>25.44242266257267</v>
+        <v>27.09593705181401</v>
       </c>
       <c r="M67" t="n">
-        <v>25.29375802485699</v>
+        <v>27.12370763736967</v>
       </c>
       <c r="N67" t="n">
         <v>32</v>
@@ -4784,7 +4784,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>14_a</t>
+          <t>2_b</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -4803,19 +4803,19 @@
         <v>2045</v>
       </c>
       <c r="I69" t="n">
-        <v>78.24018961694998</v>
+        <v>76.39458196087037</v>
       </c>
       <c r="J69" t="n">
-        <v>78.24018961694998</v>
+        <v>76.39458196087037</v>
       </c>
       <c r="K69" t="n">
         <v>100</v>
       </c>
       <c r="L69" t="n">
-        <v>32.33945620699593</v>
+        <v>29.55171992167623</v>
       </c>
       <c r="M69" t="n">
-        <v>31.64011030605105</v>
+        <v>28.95222400973573</v>
       </c>
       <c r="N69" t="n">
         <v>32</v>
@@ -4840,11 +4840,11 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>31_a</t>
+          <t>14_a</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E70" t="b">
         <v>1</v>
@@ -4853,32 +4853,32 @@
         <v>1</v>
       </c>
       <c r="G70" t="n">
-        <v>2050</v>
+        <v>2045</v>
       </c>
       <c r="H70" t="n">
-        <v>2050</v>
+        <v>2045</v>
       </c>
       <c r="I70" t="n">
-        <v>96.01490431867812</v>
+        <v>78.24018961694998</v>
       </c>
       <c r="J70" t="n">
-        <v>96.01490431867812</v>
+        <v>78.24018961694998</v>
       </c>
       <c r="K70" t="n">
         <v>100</v>
       </c>
       <c r="L70" t="n">
-        <v>36.28255339045213</v>
+        <v>32.33945620699593</v>
       </c>
       <c r="M70" t="n">
-        <v>36.6839072972405</v>
+        <v>31.64011030605105</v>
       </c>
       <c r="N70" t="n">
         <v>32</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Pressure only</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="P70" t="inlineStr"/>
@@ -4896,11 +4896,11 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2_b</t>
+          <t>31_a</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E71" t="b">
         <v>1</v>
@@ -4909,32 +4909,32 @@
         <v>1</v>
       </c>
       <c r="G71" t="n">
-        <v>2045</v>
+        <v>2050</v>
       </c>
       <c r="H71" t="n">
-        <v>2045</v>
+        <v>2050</v>
       </c>
       <c r="I71" t="n">
-        <v>76.39458196087037</v>
+        <v>96.01490431867812</v>
       </c>
       <c r="J71" t="n">
-        <v>76.39458196087037</v>
+        <v>96.01490431867812</v>
       </c>
       <c r="K71" t="n">
         <v>100</v>
       </c>
       <c r="L71" t="n">
-        <v>29.55171992167623</v>
+        <v>36.28255339045213</v>
       </c>
       <c r="M71" t="n">
-        <v>28.95222400973573</v>
+        <v>36.6839072972405</v>
       </c>
       <c r="N71" t="n">
         <v>32</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Pressure only</t>
         </is>
       </c>
       <c r="P71" t="inlineStr"/>
@@ -4952,11 +4952,11 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>25_a</t>
+          <t>13_b</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E72" t="b">
         <v>0</v>
@@ -4965,25 +4965,25 @@
         <v>1</v>
       </c>
       <c r="G72" t="n">
-        <v>2040</v>
+        <v>2050</v>
       </c>
       <c r="H72" t="n">
-        <v>2040</v>
+        <v>2050</v>
       </c>
       <c r="I72" t="n">
-        <v>87.38150101973842</v>
+        <v>84.59563676007966</v>
       </c>
       <c r="J72" t="n">
-        <v>87.38150101973842</v>
+        <v>84.59563676007966</v>
       </c>
       <c r="K72" t="n">
         <v>100</v>
       </c>
       <c r="L72" t="n">
-        <v>27.09593705181401</v>
+        <v>25.44242266257289</v>
       </c>
       <c r="M72" t="n">
-        <v>27.12370763736967</v>
+        <v>25.29375802485721</v>
       </c>
       <c r="N72" t="n">
         <v>32</v>
@@ -5008,11 +5008,11 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>13_b</t>
+          <t>25_a</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E73" t="b">
         <v>0</v>
@@ -5021,25 +5021,25 @@
         <v>1</v>
       </c>
       <c r="G73" t="n">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="H73" t="n">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="I73" t="n">
-        <v>84.59563676007966</v>
+        <v>87.38150101973842</v>
       </c>
       <c r="J73" t="n">
-        <v>84.59563676007966</v>
+        <v>87.38150101973842</v>
       </c>
       <c r="K73" t="n">
         <v>100</v>
       </c>
       <c r="L73" t="n">
-        <v>25.44242266257289</v>
+        <v>27.09593705181401</v>
       </c>
       <c r="M73" t="n">
-        <v>25.29375802485721</v>
+        <v>27.12370763736967</v>
       </c>
       <c r="N73" t="n">
         <v>32</v>
@@ -5124,14 +5124,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>14_a</t>
+          <t>2_b</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F75" t="n">
         <v>1</v>
@@ -5143,19 +5143,19 @@
         <v>2050</v>
       </c>
       <c r="I75" t="n">
-        <v>76.97104401094329</v>
+        <v>76.39458196087037</v>
       </c>
       <c r="J75" t="n">
-        <v>76.97104401094329</v>
+        <v>76.39458196087037</v>
       </c>
       <c r="K75" t="n">
         <v>100</v>
       </c>
       <c r="L75" t="n">
-        <v>25.4791129998713</v>
+        <v>29.55171992167623</v>
       </c>
       <c r="M75" t="n">
-        <v>23.53838500964068</v>
+        <v>28.95222400973573</v>
       </c>
       <c r="N75" t="n">
         <v>32</v>
@@ -5180,7 +5180,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>31_a</t>
+          <t>14_a</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -5193,25 +5193,25 @@
         <v>1</v>
       </c>
       <c r="G76" t="n">
-        <v>2040</v>
+        <v>2050</v>
       </c>
       <c r="H76" t="n">
-        <v>2040</v>
+        <v>2050</v>
       </c>
       <c r="I76" t="n">
-        <v>94.08777135878756</v>
+        <v>76.97104401094329</v>
       </c>
       <c r="J76" t="n">
-        <v>94.08777135878756</v>
+        <v>76.97104401094329</v>
       </c>
       <c r="K76" t="n">
         <v>100</v>
       </c>
       <c r="L76" t="n">
-        <v>32.08262364503698</v>
+        <v>25.4791129998713</v>
       </c>
       <c r="M76" t="n">
-        <v>26.10570821868824</v>
+        <v>23.53838500964068</v>
       </c>
       <c r="N76" t="n">
         <v>32</v>
@@ -5236,11 +5236,11 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>65_b</t>
+          <t>31_a</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E77" t="b">
         <v>0</v>
@@ -5249,25 +5249,25 @@
         <v>1</v>
       </c>
       <c r="G77" t="n">
-        <v>2045</v>
+        <v>2040</v>
       </c>
       <c r="H77" t="n">
-        <v>2045</v>
+        <v>2040</v>
       </c>
       <c r="I77" t="n">
-        <v>50.00000000000003</v>
+        <v>94.08777135878756</v>
       </c>
       <c r="J77" t="n">
-        <v>50.00000000000003</v>
+        <v>94.08777135878756</v>
       </c>
       <c r="K77" t="n">
         <v>100</v>
       </c>
       <c r="L77" t="n">
-        <v>26.76040136691488</v>
+        <v>32.08262364503698</v>
       </c>
       <c r="M77" t="n">
-        <v>22.34896224971083</v>
+        <v>26.10570821868824</v>
       </c>
       <c r="N77" t="n">
         <v>32</v>
@@ -5292,11 +5292,11 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2_b</t>
+          <t>61_a</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E78" t="b">
         <v>1</v>
@@ -5311,19 +5311,19 @@
         <v>2050</v>
       </c>
       <c r="I78" t="n">
-        <v>76.39458196087037</v>
+        <v>83.98800344108297</v>
       </c>
       <c r="J78" t="n">
-        <v>76.39458196087037</v>
+        <v>83.98800344108297</v>
       </c>
       <c r="K78" t="n">
         <v>100</v>
       </c>
       <c r="L78" t="n">
-        <v>29.55171992167623</v>
+        <v>29.81684785510058</v>
       </c>
       <c r="M78" t="n">
-        <v>28.95222400973573</v>
+        <v>30.51343096223421</v>
       </c>
       <c r="N78" t="n">
         <v>32</v>
@@ -5348,11 +5348,11 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>25_a</t>
+          <t>65_b</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E79" t="b">
         <v>0</v>
@@ -5367,19 +5367,19 @@
         <v>2045</v>
       </c>
       <c r="I79" t="n">
-        <v>87.38150101973842</v>
+        <v>50.00000000000003</v>
       </c>
       <c r="J79" t="n">
-        <v>87.38150101973842</v>
+        <v>50.00000000000003</v>
       </c>
       <c r="K79" t="n">
         <v>100</v>
       </c>
       <c r="L79" t="n">
-        <v>27.09593705181401</v>
+        <v>26.76040136691488</v>
       </c>
       <c r="M79" t="n">
-        <v>27.12370763736967</v>
+        <v>22.34896224971083</v>
       </c>
       <c r="N79" t="n">
         <v>32</v>
@@ -5404,38 +5404,38 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>61_a</t>
+          <t>25_a</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="E80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F80" t="n">
         <v>1</v>
       </c>
       <c r="G80" t="n">
-        <v>2050</v>
+        <v>2045</v>
       </c>
       <c r="H80" t="n">
-        <v>2050</v>
+        <v>2045</v>
       </c>
       <c r="I80" t="n">
-        <v>83.98800344108297</v>
+        <v>87.38150101973842</v>
       </c>
       <c r="J80" t="n">
-        <v>83.98800344108297</v>
+        <v>87.38150101973842</v>
       </c>
       <c r="K80" t="n">
         <v>100</v>
       </c>
       <c r="L80" t="n">
-        <v>29.81684785510058</v>
+        <v>27.09593705181401</v>
       </c>
       <c r="M80" t="n">
-        <v>30.51343096223421</v>
+        <v>27.12370763736967</v>
       </c>
       <c r="N80" t="n">
         <v>32</v>
@@ -5460,38 +5460,38 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>14_a</t>
+          <t>2_b</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F81" t="n">
         <v>1</v>
       </c>
       <c r="G81" t="n">
-        <v>2030</v>
+        <v>2045</v>
       </c>
       <c r="H81" t="n">
-        <v>2030</v>
+        <v>2045</v>
       </c>
       <c r="I81" t="n">
-        <v>76.97104401094329</v>
+        <v>76.39458196087037</v>
       </c>
       <c r="J81" t="n">
-        <v>76.97104401094329</v>
+        <v>76.39458196087037</v>
       </c>
       <c r="K81" t="n">
         <v>100</v>
       </c>
       <c r="L81" t="n">
-        <v>25.4791129998713</v>
+        <v>29.55171992167623</v>
       </c>
       <c r="M81" t="n">
-        <v>23.53838500964068</v>
+        <v>28.95222400973573</v>
       </c>
       <c r="N81" t="n">
         <v>32</v>
@@ -5516,45 +5516,45 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>31_a</t>
+          <t>14_a</t>
         </is>
       </c>
       <c r="D82" t="n">
         <v>30</v>
       </c>
       <c r="E82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
         <v>1</v>
       </c>
       <c r="G82" t="n">
-        <v>2050</v>
+        <v>2030</v>
       </c>
       <c r="H82" t="n">
-        <v>2050</v>
+        <v>2030</v>
       </c>
       <c r="I82" t="n">
-        <v>96.01490431867812</v>
+        <v>76.97104401094329</v>
       </c>
       <c r="J82" t="n">
-        <v>96.01490431867812</v>
+        <v>76.97104401094329</v>
       </c>
       <c r="K82" t="n">
         <v>100</v>
       </c>
       <c r="L82" t="n">
-        <v>36.28255339045213</v>
+        <v>25.4791129998713</v>
       </c>
       <c r="M82" t="n">
-        <v>36.6839072972405</v>
+        <v>23.53838500964068</v>
       </c>
       <c r="N82" t="n">
         <v>32</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>Pressure only</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="P82" t="inlineStr"/>
@@ -5572,11 +5572,11 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2_b</t>
+          <t>31_a</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E83" t="b">
         <v>1</v>
@@ -5585,32 +5585,32 @@
         <v>1</v>
       </c>
       <c r="G83" t="n">
-        <v>2045</v>
+        <v>2050</v>
       </c>
       <c r="H83" t="n">
-        <v>2045</v>
+        <v>2050</v>
       </c>
       <c r="I83" t="n">
-        <v>76.39458196087037</v>
+        <v>96.01490431867812</v>
       </c>
       <c r="J83" t="n">
-        <v>76.39458196087037</v>
+        <v>96.01490431867812</v>
       </c>
       <c r="K83" t="n">
         <v>100</v>
       </c>
       <c r="L83" t="n">
-        <v>29.55171992167623</v>
+        <v>36.28255339045213</v>
       </c>
       <c r="M83" t="n">
-        <v>28.95222400973573</v>
+        <v>36.6839072972405</v>
       </c>
       <c r="N83" t="n">
         <v>32</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Pressure only</t>
         </is>
       </c>
       <c r="P83" t="inlineStr"/>
@@ -5628,11 +5628,11 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>25_a</t>
+          <t>13_b</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E84" t="b">
         <v>0</v>
@@ -5641,25 +5641,25 @@
         <v>1</v>
       </c>
       <c r="G84" t="n">
-        <v>2045</v>
+        <v>2050</v>
       </c>
       <c r="H84" t="n">
-        <v>2045</v>
+        <v>2050</v>
       </c>
       <c r="I84" t="n">
-        <v>87.38150101973842</v>
+        <v>65.09457797059358</v>
       </c>
       <c r="J84" t="n">
-        <v>87.38150101973842</v>
+        <v>65.09457797059358</v>
       </c>
       <c r="K84" t="n">
         <v>100</v>
       </c>
       <c r="L84" t="n">
-        <v>27.09593705181401</v>
+        <v>24.63421202281575</v>
       </c>
       <c r="M84" t="n">
-        <v>27.12370763736967</v>
+        <v>24.48554738510007</v>
       </c>
       <c r="N84" t="n">
         <v>32</v>
@@ -5684,11 +5684,11 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>13_b</t>
+          <t>25_a</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E85" t="b">
         <v>0</v>
@@ -5697,25 +5697,25 @@
         <v>1</v>
       </c>
       <c r="G85" t="n">
-        <v>2050</v>
+        <v>2045</v>
       </c>
       <c r="H85" t="n">
-        <v>2050</v>
+        <v>2045</v>
       </c>
       <c r="I85" t="n">
-        <v>65.09457797059358</v>
+        <v>87.38150101973842</v>
       </c>
       <c r="J85" t="n">
-        <v>65.09457797059358</v>
+        <v>87.38150101973842</v>
       </c>
       <c r="K85" t="n">
         <v>100</v>
       </c>
       <c r="L85" t="n">
-        <v>24.63421202281575</v>
+        <v>27.09593705181401</v>
       </c>
       <c r="M85" t="n">
-        <v>24.48554738510007</v>
+        <v>27.12370763736967</v>
       </c>
       <c r="N85" t="n">
         <v>32</v>
@@ -5800,11 +5800,11 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>14_a</t>
+          <t>2_b</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="E87" t="b">
         <v>0</v>
@@ -5813,25 +5813,25 @@
         <v>1</v>
       </c>
       <c r="G87" t="n">
-        <v>2040</v>
+        <v>2045</v>
       </c>
       <c r="H87" t="n">
-        <v>2040</v>
+        <v>2045</v>
       </c>
       <c r="I87" t="n">
-        <v>76.97104401094329</v>
+        <v>87.93509768253111</v>
       </c>
       <c r="J87" t="n">
-        <v>76.97104401094329</v>
+        <v>87.93509768253111</v>
       </c>
       <c r="K87" t="n">
         <v>100</v>
       </c>
       <c r="L87" t="n">
-        <v>25.4791129998713</v>
+        <v>23.19354690367037</v>
       </c>
       <c r="M87" t="n">
-        <v>23.53838500964068</v>
+        <v>22.45514163646351</v>
       </c>
       <c r="N87" t="n">
         <v>32</v>
@@ -5856,7 +5856,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>31_a</t>
+          <t>14_a</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -5869,25 +5869,25 @@
         <v>1</v>
       </c>
       <c r="G88" t="n">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="H88" t="n">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="I88" t="n">
-        <v>94.08777135878756</v>
+        <v>76.97104401094329</v>
       </c>
       <c r="J88" t="n">
-        <v>94.08777135878756</v>
+        <v>76.97104401094329</v>
       </c>
       <c r="K88" t="n">
         <v>100</v>
       </c>
       <c r="L88" t="n">
-        <v>32.08262364503698</v>
+        <v>25.4791129998713</v>
       </c>
       <c r="M88" t="n">
-        <v>26.10570821868824</v>
+        <v>23.53838500964068</v>
       </c>
       <c r="N88" t="n">
         <v>32</v>
@@ -5912,11 +5912,11 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>65_b</t>
+          <t>31_a</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E89" t="b">
         <v>0</v>
@@ -5931,19 +5931,19 @@
         <v>2050</v>
       </c>
       <c r="I89" t="n">
-        <v>86.95400932730499</v>
+        <v>94.08777135878756</v>
       </c>
       <c r="J89" t="n">
-        <v>86.95400932730499</v>
+        <v>94.08777135878756</v>
       </c>
       <c r="K89" t="n">
         <v>100</v>
       </c>
       <c r="L89" t="n">
-        <v>32.62473401350245</v>
+        <v>32.08262364503698</v>
       </c>
       <c r="M89" t="n">
-        <v>25.56814634261212</v>
+        <v>26.10570821868824</v>
       </c>
       <c r="N89" t="n">
         <v>32</v>
@@ -5968,11 +5968,11 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>5_a</t>
+          <t>59_a</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E90" t="b">
         <v>0</v>
@@ -5981,25 +5981,25 @@
         <v>1</v>
       </c>
       <c r="G90" t="n">
-        <v>2040</v>
+        <v>2050</v>
       </c>
       <c r="H90" t="n">
         <v>2050</v>
       </c>
       <c r="I90" t="n">
-        <v>113.3821431187982</v>
+        <v>66.22090372966993</v>
       </c>
       <c r="J90" t="n">
-        <v>113.3821431187982</v>
+        <v>66.22090372966993</v>
       </c>
       <c r="K90" t="n">
         <v>100</v>
       </c>
       <c r="L90" t="n">
-        <v>35.77408120748448</v>
+        <v>22.24172757881252</v>
       </c>
       <c r="M90" t="n">
-        <v>35.14591303475528</v>
+        <v>22.23426138103358</v>
       </c>
       <c r="N90" t="n">
         <v>32</v>
@@ -6009,11 +6009,7 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="P90" t="inlineStr">
-        <is>
-          <t>Shared-node effect: this pipe is a non-dominant supplier at node 23; without its booster its own pi_dest/theta_dest (142 bar / 37°C) would fall outside the required +/-30 bar / +/-5°C tolerance band around the node's 184 bar / 52°C.</t>
-        </is>
-      </c>
+      <c r="P90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -6028,11 +6024,11 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2_b</t>
+          <t>65_b</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="E91" t="b">
         <v>0</v>
@@ -6041,25 +6037,25 @@
         <v>1</v>
       </c>
       <c r="G91" t="n">
-        <v>2045</v>
+        <v>2050</v>
       </c>
       <c r="H91" t="n">
-        <v>2045</v>
+        <v>2050</v>
       </c>
       <c r="I91" t="n">
-        <v>87.93509768253111</v>
+        <v>86.95400932730499</v>
       </c>
       <c r="J91" t="n">
-        <v>87.93509768253111</v>
+        <v>86.95400932730499</v>
       </c>
       <c r="K91" t="n">
         <v>100</v>
       </c>
       <c r="L91" t="n">
-        <v>23.19354690367037</v>
+        <v>32.62473401350245</v>
       </c>
       <c r="M91" t="n">
-        <v>22.45514163646351</v>
+        <v>25.56814634261212</v>
       </c>
       <c r="N91" t="n">
         <v>32</v>
@@ -6140,11 +6136,11 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>59_a</t>
+          <t>10_a</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="E93" t="b">
         <v>0</v>
@@ -6153,32 +6149,32 @@
         <v>1</v>
       </c>
       <c r="G93" t="n">
-        <v>2050</v>
+        <v>2030</v>
       </c>
       <c r="H93" t="n">
-        <v>2050</v>
+        <v>2030</v>
       </c>
       <c r="I93" t="n">
-        <v>66.22090372966993</v>
+        <v>123.1245526439649</v>
       </c>
       <c r="J93" t="n">
-        <v>66.22090372966993</v>
+        <v>122.869494826188</v>
       </c>
       <c r="K93" t="n">
         <v>100</v>
       </c>
       <c r="L93" t="n">
-        <v>22.24172757881252</v>
+        <v>23.21269847782931</v>
       </c>
       <c r="M93" t="n">
-        <v>22.23426138103358</v>
+        <v>23.46148378669019</v>
       </c>
       <c r="N93" t="n">
         <v>32</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Temperature only</t>
         </is>
       </c>
       <c r="P93" t="inlineStr"/>
@@ -6196,11 +6192,11 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>10_a</t>
+          <t>5_a</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E94" t="b">
         <v>0</v>
@@ -6209,35 +6205,39 @@
         <v>1</v>
       </c>
       <c r="G94" t="n">
-        <v>2030</v>
+        <v>2040</v>
       </c>
       <c r="H94" t="n">
-        <v>2030</v>
+        <v>2050</v>
       </c>
       <c r="I94" t="n">
-        <v>123.1245526439649</v>
+        <v>113.3821431187982</v>
       </c>
       <c r="J94" t="n">
-        <v>122.869494826188</v>
+        <v>113.3821431187982</v>
       </c>
       <c r="K94" t="n">
         <v>100</v>
       </c>
       <c r="L94" t="n">
-        <v>23.21269847782931</v>
+        <v>35.77408120748448</v>
       </c>
       <c r="M94" t="n">
-        <v>23.46148378669019</v>
+        <v>35.14591303475528</v>
       </c>
       <c r="N94" t="n">
         <v>32</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>Temperature only</t>
-        </is>
-      </c>
-      <c r="P94" t="inlineStr"/>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Shared-node effect: this pipe is a non-dominant supplier at node 23; without its booster its own pi_dest/theta_dest (142 bar / 37°C) would fall outside the required +/-30 bar / +/-5°C tolerance band around the node's 184 bar / 52°C.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
